--- a/catalogue_v1.xlsx
+++ b/catalogue_v1.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="43">
   <si>
     <t xml:space="preserve">Serial Number</t>
   </si>
@@ -203,42 +203,6 @@
   </si>
   <si>
     <t xml:space="preserve">Knill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quiet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Why I’m Like Dad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luchnik</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How Not to be Wrong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ellenberg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Art of Thinking Clearly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dobelli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Why We Sleep</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thinking, Fast and Slow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kahnemann</t>
   </si>
 </sst>
 </file>
@@ -335,21 +299,17 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -555,444 +515,337 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="38.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="25.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="27.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="4" width="27.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="27.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="27.1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="4" t="n">
+      <c r="D2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>699</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="3" t="n">
         <v>1299</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="4" t="n">
+      <c r="D4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>899</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="3" t="n">
         <v>599</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="4" t="n">
+      <c r="D6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>599</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="4" t="n">
+      <c r="D7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="3" t="n">
         <v>299</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="7" t="s">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="3" t="n">
         <v>599</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="4" t="n">
+      <c r="D9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="3" t="n">
         <v>699</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="3" t="n">
         <v>1599</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="3" t="n">
         <v>399</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="4" t="n">
+      <c r="D12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="3" t="n">
         <v>499</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="3" t="n">
         <v>599</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="4" t="n">
+      <c r="D14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="3" t="n">
         <v>799</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="4" t="n">
+      <c r="D15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="3" t="n">
         <v>599</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="4" t="n">
+      <c r="D16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="3" t="n">
         <v>499</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="4" t="n">
+      <c r="D17" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="3" t="n">
         <v>1399</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="4" t="n">
+      <c r="D18" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="3" t="n">
         <v>1299</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="3" t="n">
         <v>799</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="n">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
